--- a/Informes_mensualizados_template.xlsx
+++ b/Informes_mensualizados_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizma\Documents\Informes-JSalazar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA85C79B-107F-4A43-8D31-E22132107C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114DE266-7DA3-43E9-8159-170ACE1F42E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1080" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C19F3370-E4BE-428B-B8B1-0897F0CE56CF}"/>
   </bookViews>
@@ -538,11 +538,11 @@
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="#,##0_ ;\-#,##0\ "/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@"/>
-    <numFmt numFmtId="171" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
+    <numFmt numFmtId="166" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -1071,7 +1071,7 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1094,51 +1094,51 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="17" fontId="4" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1146,25 +1146,25 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="8" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="5" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1179,91 +1179,91 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="4" borderId="23" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="4" borderId="23" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="21" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="21" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="25" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="14" fillId="7" borderId="26" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="14" fillId="7" borderId="26" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="7" borderId="27" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="14" fillId="7" borderId="27" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="16" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="16" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="28" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="11" fillId="3" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="11" fillId="3" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="3" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="14" fillId="3" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="28" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="14" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="14" fillId="8" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="8" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="14" fillId="8" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="28" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="14" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="14" fillId="10" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="10" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="14" fillId="10" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="25" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="17" fillId="7" borderId="26" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="17" fillId="7" borderId="26" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="4" borderId="27" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="17" fillId="4" borderId="27" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="5" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="18" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="18" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="19" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="19" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1271,12 +1271,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="18" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="7" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1293,6 +1287,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="21" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2461,34 +2461,34 @@
   <sheetData>
     <row r="1" spans="1:37" ht="13" x14ac:dyDescent="0.3">
       <c r="B1" s="3"/>
-      <c r="C1" s="116" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="116" t="s">
+      <c r="C1" s="122" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="123"/>
+      <c r="O1" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
+      <c r="P1" s="123"/>
+      <c r="Q1" s="123"/>
+      <c r="R1" s="123"/>
+      <c r="S1" s="123"/>
+      <c r="T1" s="123"/>
+      <c r="U1" s="123"/>
+      <c r="V1" s="123"/>
+      <c r="W1" s="123"/>
+      <c r="X1" s="123"/>
+      <c r="Y1" s="123"/>
+      <c r="Z1" s="123"/>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
@@ -9030,71 +9030,71 @@
       <c r="B1" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="118" t="s">
+      <c r="C1" s="116" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="118" t="s">
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="116" t="s">
         <v>92</v>
       </c>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="120"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="118"/>
     </row>
     <row r="2" spans="1:30" ht="15" x14ac:dyDescent="0.3">
       <c r="B2" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="121" t="s">
+      <c r="C2" s="119" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="122"/>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
-      <c r="G2" s="122"/>
-      <c r="H2" s="122"/>
-      <c r="I2" s="122"/>
-      <c r="J2" s="122"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="122"/>
-      <c r="O2" s="123"/>
-      <c r="P2" s="121" t="s">
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="121"/>
+      <c r="P2" s="119" t="s">
         <v>95</v>
       </c>
-      <c r="Q2" s="122"/>
-      <c r="R2" s="122"/>
-      <c r="S2" s="122"/>
-      <c r="T2" s="122"/>
-      <c r="U2" s="122"/>
-      <c r="V2" s="122"/>
-      <c r="W2" s="122"/>
-      <c r="X2" s="122"/>
-      <c r="Y2" s="122"/>
-      <c r="Z2" s="122"/>
-      <c r="AA2" s="122"/>
-      <c r="AB2" s="123"/>
+      <c r="Q2" s="120"/>
+      <c r="R2" s="120"/>
+      <c r="S2" s="120"/>
+      <c r="T2" s="120"/>
+      <c r="U2" s="120"/>
+      <c r="V2" s="120"/>
+      <c r="W2" s="120"/>
+      <c r="X2" s="120"/>
+      <c r="Y2" s="120"/>
+      <c r="Z2" s="120"/>
+      <c r="AA2" s="120"/>
+      <c r="AB2" s="121"/>
     </row>
     <row r="3" spans="1:30" s="71" customFormat="1" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A3" s="72"/>
@@ -9285,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="81">
-        <f>SUM(C5:N5)</f>
+        <f>SUM(O6:O11)</f>
         <v>0</v>
       </c>
       <c r="P5" s="80">

--- a/Informes_mensualizados_template.xlsx
+++ b/Informes_mensualizados_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizma\Documents\Informes-JSalazar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114DE266-7DA3-43E9-8159-170ACE1F42E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815F57B8-48AE-41BB-8B4D-C11AF324E25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1080" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C19F3370-E4BE-428B-B8B1-0897F0CE56CF}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C19F3370-E4BE-428B-B8B1-0897F0CE56CF}"/>
   </bookViews>
   <sheets>
     <sheet name="BCE" sheetId="1" r:id="rId1"/>
@@ -12993,7 +12993,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="111">
-        <f>-BCE!P69+BCE!O69-O75</f>
+        <f>+O79-BCE!N69</f>
         <v>0</v>
       </c>
       <c r="P83" s="111">
